--- a/grupos/4APM - Estadisticos 20222.xlsx
+++ b/grupos/4APM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -180,12 +180,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
@@ -246,6 +246,9 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -294,6 +297,9 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
@@ -369,6 +375,9 @@
     <t>JOCELIN</t>
   </si>
   <si>
+    <t>AOLANI ALINE</t>
+  </si>
+  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
@@ -397,15 +406,6 @@
   </si>
   <si>
     <t>PAULA MARIA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>AOLANI ALINE</t>
   </si>
 </sst>
 </file>
@@ -922,7 +922,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -985,7 +985,7 @@
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>6</v>
@@ -1011,7 +1011,7 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>9</v>
@@ -1074,7 +1074,7 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>9</v>
@@ -1100,7 +1100,7 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -1163,7 +1163,7 @@
         <v>5</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1189,7 +1189,7 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -1252,7 +1252,7 @@
         <v>5</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1278,7 +1278,7 @@
         <v>8</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -1341,7 +1341,7 @@
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1367,7 +1367,7 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -1430,7 +1430,7 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>7</v>
@@ -1456,7 +1456,7 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H10">
         <v>8</v>
@@ -1519,7 +1519,7 @@
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1545,7 +1545,7 @@
         <v>9</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H11">
         <v>8</v>
@@ -1608,7 +1608,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1634,7 +1634,7 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -1697,7 +1697,7 @@
         <v>10</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>10</v>
@@ -1723,7 +1723,7 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H13">
         <v>10</v>
@@ -1786,7 +1786,7 @@
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>10</v>
@@ -1812,7 +1812,7 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H14">
         <v>8</v>
@@ -1875,7 +1875,7 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1901,7 +1901,7 @@
         <v>7</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H15">
         <v>7</v>
@@ -1964,7 +1964,7 @@
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>7</v>
@@ -1990,7 +1990,7 @@
         <v>7</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>7</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H17">
         <v>10</v>
@@ -2142,7 +2142,7 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2168,7 +2168,7 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H18">
         <v>8</v>
@@ -2231,7 +2231,7 @@
         <v>10</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2257,7 +2257,7 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H19">
         <v>8</v>
@@ -2320,7 +2320,7 @@
         <v>10</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -2399,7 +2399,7 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -2462,7 +2462,7 @@
         <v>6</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>6</v>
@@ -2488,7 +2488,7 @@
         <v>9</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H22">
         <v>6</v>
@@ -2551,7 +2551,7 @@
         <v>9</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>6</v>
@@ -2577,7 +2577,7 @@
         <v>9</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H23">
         <v>10</v>
@@ -2640,7 +2640,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2666,7 +2666,7 @@
         <v>9</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>10</v>
@@ -2755,7 +2755,7 @@
         <v>9</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -2818,7 +2818,7 @@
         <v>9</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>5</v>
@@ -2844,7 +2844,7 @@
         <v>10</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H26">
         <v>9</v>
@@ -2907,7 +2907,7 @@
         <v>10</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -2933,7 +2933,7 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>9</v>
@@ -2996,7 +2996,7 @@
         <v>10</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>9</v>
@@ -3022,7 +3022,7 @@
         <v>9</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H28">
         <v>10</v>
@@ -3085,7 +3085,7 @@
         <v>9</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>10</v>
@@ -3111,7 +3111,7 @@
         <v>10</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>10</v>
@@ -3174,7 +3174,7 @@
         <v>10</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>10</v>
@@ -3200,7 +3200,7 @@
         <v>7</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -3263,7 +3263,7 @@
         <v>7</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC30">
         <v>5</v>
@@ -3289,7 +3289,7 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>10</v>
@@ -3352,7 +3352,7 @@
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3494,13 +3494,13 @@
         <v>96.7</v>
       </c>
       <c r="E4">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>106.7</v>
@@ -3562,13 +3562,13 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>106.7</v>
@@ -3630,13 +3630,13 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>106.7</v>
@@ -3698,13 +3698,13 @@
         <v>86.7</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="F7">
         <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>106.7</v>
@@ -3766,13 +3766,13 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>106.7</v>
@@ -3834,13 +3834,13 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>106.7</v>
@@ -3902,13 +3902,13 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>106.7</v>
@@ -3970,13 +3970,13 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>100</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>106.7</v>
@@ -4038,13 +4038,13 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12">
         <v>106.7</v>
@@ -4106,13 +4106,13 @@
         <v>93.3</v>
       </c>
       <c r="E13">
-        <v>113.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F13">
         <v>100</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>106.7</v>
@@ -4174,13 +4174,13 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14">
         <v>106.7</v>
@@ -4242,13 +4242,13 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>100</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15">
         <v>106.7</v>
@@ -4310,13 +4310,13 @@
         <v>96.7</v>
       </c>
       <c r="E16">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>100</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>106.7</v>
@@ -4378,13 +4378,13 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
         <v>106.7</v>
@@ -4446,13 +4446,13 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>106.7</v>
@@ -4514,13 +4514,13 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>106.7</v>
@@ -4623,13 +4623,13 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21">
         <v>106.7</v>
@@ -4691,13 +4691,13 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>106.7</v>
@@ -4759,13 +4759,13 @@
         <v>93.3</v>
       </c>
       <c r="E23">
-        <v>113.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F23">
         <v>100</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23">
         <v>106.7</v>
@@ -4827,13 +4827,13 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24">
         <v>106.7</v>
@@ -4895,13 +4895,13 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>110</v>
+        <v>94.3</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>106.7</v>
@@ -4963,13 +4963,13 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>106.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26">
         <v>106.7</v>
@@ -5031,13 +5031,13 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27">
         <v>106.7</v>
@@ -5099,13 +5099,13 @@
         <v>96.7</v>
       </c>
       <c r="E28">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>100</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28">
         <v>106.7</v>
@@ -5167,13 +5167,13 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>106.7</v>
@@ -5235,13 +5235,13 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30">
         <v>106.7</v>
@@ -5303,13 +5303,13 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>116.7</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>100</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>106.7</v>
@@ -5409,7 +5409,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -5418,48 +5418,51 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>66.67</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G3">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5470,28 +5473,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>85.70999999999999</v>
+        <v>92.59</v>
       </c>
       <c r="G4">
-        <v>14.29</v>
+        <v>7.41</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5502,28 +5505,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="G5">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5534,28 +5537,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>28</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>92.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="G6">
-        <v>7.14</v>
+        <v>3.57</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5566,25 +5569,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>27</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>96.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>8.300000000000001</v>
@@ -5635,7 +5638,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5660,546 +5663,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920331</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920332</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920333</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920334</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920335</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920137</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920336</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920338</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920339</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920340</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920343</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920341</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920342</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920343</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920344</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920345</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
-        <v>115</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920347</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920348</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920349</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920350</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" t="s">
-        <v>119</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920149</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920351</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920322</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920174</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920352</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920353</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" t="s">
-        <v>124</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920354</v>
-      </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s">
-        <v>125</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -6241,13 +5704,13 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6258,13 +5721,13 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6275,13 +5738,13 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6292,13 +5755,13 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6309,13 +5772,13 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6329,10 +5792,10 @@
         <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6346,10 +5809,10 @@
         <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6360,13 +5823,13 @@
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6377,13 +5840,13 @@
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6394,13 +5857,13 @@
         <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6414,10 +5877,10 @@
         <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6431,10 +5894,10 @@
         <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6448,10 +5911,10 @@
         <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6462,13 +5925,13 @@
         <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6482,10 +5945,10 @@
         <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6496,154 +5959,154 @@
         <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920347</v>
+        <v>20330061460280</v>
       </c>
       <c r="B18" t="s">
         <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920348</v>
+        <v>21330051920347</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920349</v>
+        <v>21330051920348</v>
       </c>
       <c r="B20" t="s">
         <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920350</v>
+        <v>21330051920349</v>
       </c>
       <c r="B21" t="s">
         <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920149</v>
+        <v>21330051920350</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920351</v>
+        <v>21330051920149</v>
       </c>
       <c r="B23" t="s">
         <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920322</v>
+        <v>21330051920351</v>
       </c>
       <c r="B24" t="s">
         <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920174</v>
+        <v>21330051920322</v>
       </c>
       <c r="B25" t="s">
         <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920352</v>
+        <v>21330051920174</v>
       </c>
       <c r="B26" t="s">
         <v>82</v>
@@ -6652,55 +6115,55 @@
         <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920353</v>
+        <v>21330051920352</v>
       </c>
       <c r="B27" t="s">
         <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920354</v>
+        <v>21330051920353</v>
       </c>
       <c r="B28" t="s">
         <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330061460280</v>
+        <v>21330051920354</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
         <v>128</v>
@@ -6716,7 +6179,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6748,22 +6211,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920331</v>
+        <v>21330051920332</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6771,45 +6234,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920331</v>
+        <v>21330051920332</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920335</v>
+        <v>21330051920149</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6817,45 +6280,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920335</v>
+        <v>21330051920149</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920137</v>
+        <v>21330051920331</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6863,30 +6326,30 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920137</v>
+        <v>21330051920335</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
         <v>53</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920336</v>
+        <v>21330051920137</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -6895,13 +6358,13 @@
         <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6918,16 +6381,16 @@
         <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -6938,16 +6401,16 @@
         <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6955,508 +6418,48 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920340</v>
+        <v>21330051920347</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>53</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920347</v>
+        <v>21330051920353</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
       </c>
       <c r="G12">
         <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920347</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920353</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920353</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920333</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920338</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920339</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920343</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920341</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920342</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920343</v>
-      </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920344</v>
-      </c>
-      <c r="B23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920345</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920348</v>
-      </c>
-      <c r="B25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" t="s">
-        <v>117</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920349</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920350</v>
-      </c>
-      <c r="B27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920351</v>
-      </c>
-      <c r="B28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920322</v>
-      </c>
-      <c r="B29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" t="s">
-        <v>121</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920174</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" t="s">
-        <v>122</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920352</v>
-      </c>
-      <c r="B31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" t="s">
-        <v>123</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920354</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4APM - Estadisticos 20222.xlsx
+++ b/grupos/4APM - Estadisticos 20222.xlsx
@@ -4573,13 +4573,13 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D20">
         <v>83.3</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H20">
         <v>106.7</v>

--- a/grupos/4APM - Estadisticos 20222.xlsx
+++ b/grupos/4APM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -183,13 +183,19 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>NC</t>
@@ -5476,7 +5482,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>27</v>
@@ -5508,7 +5514,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5">
         <v>28</v>
@@ -5540,7 +5546,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>28</v>
@@ -5572,7 +5578,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>27</v>
@@ -5604,7 +5610,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>28</v>
@@ -5647,16 +5653,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5681,16 +5687,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>51</v>
@@ -5701,13 +5707,13 @@
         <v>21330051920331</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5718,13 +5724,13 @@
         <v>21330051920332</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5735,13 +5741,13 @@
         <v>21330051920333</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -5752,13 +5758,13 @@
         <v>21330051920334</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5769,13 +5775,13 @@
         <v>21330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5786,13 +5792,13 @@
         <v>21330051920137</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5803,13 +5809,13 @@
         <v>21330051920336</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5820,13 +5826,13 @@
         <v>21330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5837,13 +5843,13 @@
         <v>21330051920339</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5854,13 +5860,13 @@
         <v>21330051920340</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5871,13 +5877,13 @@
         <v>20330051920343</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -5888,13 +5894,13 @@
         <v>21330051920341</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5905,13 +5911,13 @@
         <v>21330051920342</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5922,13 +5928,13 @@
         <v>21330051920343</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5939,13 +5945,13 @@
         <v>21330051920344</v>
       </c>
       <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
         <v>73</v>
       </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5956,13 +5962,13 @@
         <v>21330051920345</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5973,13 +5979,13 @@
         <v>20330061460280</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5990,13 +5996,13 @@
         <v>21330051920347</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6007,13 +6013,13 @@
         <v>21330051920348</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6024,13 +6030,13 @@
         <v>21330051920349</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6041,13 +6047,13 @@
         <v>21330051920350</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6058,13 +6064,13 @@
         <v>21330051920149</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6075,13 +6081,13 @@
         <v>21330051920351</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6092,13 +6098,13 @@
         <v>21330051920322</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6109,13 +6115,13 @@
         <v>21330051920174</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6126,13 +6132,13 @@
         <v>21330051920352</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6143,13 +6149,13 @@
         <v>21330051920353</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6160,13 +6166,13 @@
         <v>21330051920354</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6188,16 +6194,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6214,13 +6220,13 @@
         <v>21330051920332</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6237,19 +6243,19 @@
         <v>21330051920332</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6260,13 +6266,13 @@
         <v>21330051920149</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6283,13 +6289,13 @@
         <v>21330051920149</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -6306,13 +6312,13 @@
         <v>21330051920331</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6329,13 +6335,13 @@
         <v>21330051920335</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -6352,13 +6358,13 @@
         <v>21330051920137</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6375,13 +6381,13 @@
         <v>21330051920336</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -6398,13 +6404,13 @@
         <v>21330051920340</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6421,13 +6427,13 @@
         <v>21330051920347</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -6444,13 +6450,13 @@
         <v>21330051920353</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>

--- a/grupos/4APM - Estadisticos 20222.xlsx
+++ b/grupos/4APM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -189,12 +188,12 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
@@ -210,141 +209,63 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AVELLEIRA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>ABAD</t>
   </si>
   <si>
-    <t>AVELLEIRA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARAY</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
   </si>
   <si>
     <t>MARITZA</t>
   </si>
   <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>DEBORA GEORGINA</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
     <t>NAHOMI ITZAYANA</t>
   </si>
   <si>
@@ -354,70 +275,22 @@
     <t>YAIR DAVID</t>
   </si>
   <si>
-    <t>CRISTINA KARELY</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
     <t>DARLET VICTORIA</t>
   </si>
   <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>CRISTIAN MANUEL</t>
-  </si>
-  <si>
-    <t>JONATHAN MOISES</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>JOCELIN</t>
-  </si>
-  <si>
-    <t>AOLANI ALINE</t>
-  </si>
-  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
-    <t>LUZ AMELY</t>
-  </si>
-  <si>
-    <t>SAORI</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>AMIR ALONSO</t>
-  </si>
-  <si>
-    <t>GEMMA MARIA</t>
-  </si>
-  <si>
-    <t>EYTHAN</t>
-  </si>
-  <si>
-    <t>NOEMI</t>
-  </si>
-  <si>
     <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>PAULA MARIA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -470,11 +343,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,16 +808,16 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -952,7 +826,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1023,16 +897,16 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1041,7 +915,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1065,16 +939,16 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1083,7 +957,7 @@
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1112,16 +986,16 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1130,7 +1004,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1172,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1201,16 +1075,16 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1219,7 +1093,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1252,7 +1126,7 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1290,16 +1164,16 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1308,7 +1182,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1350,7 +1224,7 @@
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1379,16 +1253,16 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1397,7 +1271,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1427,7 +1301,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z9">
         <v>9</v>
@@ -1439,7 +1313,7 @@
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1468,16 +1342,16 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1486,7 +1360,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1510,16 +1384,16 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1557,16 +1431,16 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1575,7 +1449,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1599,16 +1473,16 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1646,16 +1520,16 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1664,7 +1538,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1694,7 +1568,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>10</v>
@@ -1735,16 +1609,16 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1753,7 +1627,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1783,7 +1657,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>9</v>
@@ -1795,7 +1669,7 @@
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1824,16 +1698,16 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1842,7 +1716,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1875,7 +1749,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -1884,7 +1758,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1913,16 +1787,16 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1931,7 +1805,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2002,16 +1876,16 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2020,7 +1894,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2050,7 +1924,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>9</v>
@@ -2091,16 +1965,16 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2109,7 +1983,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2139,7 +2013,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>8</v>
@@ -2180,16 +2054,16 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2198,7 +2072,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2228,7 +2102,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <v>10</v>
@@ -2240,7 +2114,7 @@
         <v>8</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2269,16 +2143,16 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2287,7 +2161,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2311,16 +2185,16 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>10</v>
@@ -2349,16 +2223,16 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2373,7 +2247,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2411,16 +2285,16 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2429,7 +2303,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2453,16 +2327,16 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>6</v>
@@ -2500,16 +2374,16 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2518,7 +2392,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2542,16 +2416,16 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22">
         <v>9</v>
@@ -2560,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2589,16 +2463,16 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2607,7 +2481,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2637,7 +2511,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z23">
         <v>8</v>
@@ -2678,16 +2552,16 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2696,7 +2570,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2767,16 +2641,16 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2785,7 +2659,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2809,16 +2683,16 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>9</v>
@@ -2856,16 +2730,16 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2874,7 +2748,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2904,10 +2778,10 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>10</v>
@@ -2945,16 +2819,16 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2963,7 +2837,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2993,7 +2867,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z27">
         <v>10</v>
@@ -3034,16 +2908,16 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -3052,7 +2926,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3082,7 +2956,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z28">
         <v>9</v>
@@ -3123,16 +2997,16 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3141,7 +3015,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3171,7 +3045,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <v>10</v>
@@ -3212,16 +3086,16 @@
         <v>5</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3230,7 +3104,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3260,7 +3134,7 @@
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>7</v>
@@ -3301,16 +3175,16 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3319,7 +3193,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3349,7 +3223,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z31">
         <v>10</v>
@@ -3512,16 +3386,16 @@
         <v>106.7</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -3530,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -3580,16 +3454,16 @@
         <v>106.7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -3598,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -3648,16 +3522,16 @@
         <v>106.7</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -3666,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -3716,16 +3590,16 @@
         <v>106.7</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -3734,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -3784,16 +3658,16 @@
         <v>106.7</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -3802,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3852,16 +3726,16 @@
         <v>106.7</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -3870,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3920,16 +3794,16 @@
         <v>106.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -3938,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3988,16 +3862,16 @@
         <v>106.7</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -4006,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -4056,16 +3930,16 @@
         <v>106.7</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -4074,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -4124,16 +3998,16 @@
         <v>106.7</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -4142,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4192,16 +4066,16 @@
         <v>106.7</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -4210,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4260,16 +4134,16 @@
         <v>106.7</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -4278,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4328,16 +4202,16 @@
         <v>106.7</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -4346,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -4396,16 +4270,16 @@
         <v>106.7</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -4414,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4464,16 +4338,16 @@
         <v>106.7</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -4482,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4532,16 +4406,16 @@
         <v>106.7</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -4550,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4591,16 +4465,16 @@
         <v>106.7</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4641,16 +4515,16 @@
         <v>106.7</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -4659,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4709,16 +4583,16 @@
         <v>106.7</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -4727,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -4777,16 +4651,16 @@
         <v>106.7</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -4795,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -4845,16 +4719,16 @@
         <v>106.7</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -4863,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -4913,16 +4787,16 @@
         <v>106.7</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -4931,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -4981,16 +4855,16 @@
         <v>106.7</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -4999,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5049,16 +4923,16 @@
         <v>106.7</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -5067,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5117,16 +4991,16 @@
         <v>106.7</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -5135,7 +5009,7 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5185,16 +5059,16 @@
         <v>106.7</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -5203,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -5253,16 +5127,16 @@
         <v>106.7</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -5271,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -5321,16 +5195,16 @@
         <v>106.7</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -5339,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -5379,6 +5253,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5429,11 +5305,11 @@
       <c r="E2">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>66.67</v>
-      </c>
-      <c r="G2">
-        <v>33.33</v>
+      <c r="F2" s="2">
+        <v>66.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>33.3</v>
       </c>
       <c r="H2">
         <v>6.7</v>
@@ -5441,7 +5317,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5461,19 +5337,19 @@
       <c r="E3">
         <v>4</v>
       </c>
-      <c r="F3">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="G3">
-        <v>14.29</v>
+      <c r="F3" s="2">
+        <v>85.7</v>
+      </c>
+      <c r="G3" s="2">
+        <v>14.3</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5493,11 +5369,11 @@
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4">
-        <v>92.59</v>
-      </c>
-      <c r="G4">
-        <v>7.41</v>
+      <c r="F4" s="2">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="G4" s="2">
+        <v>7.4</v>
       </c>
       <c r="H4">
         <v>8.699999999999999</v>
@@ -5505,13 +5381,13 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -5525,25 +5401,25 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5">
-        <v>92.86</v>
-      </c>
-      <c r="G5">
-        <v>7.14</v>
+      <c r="F5" s="2">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7.1</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -5552,24 +5428,24 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>96.43000000000001</v>
-      </c>
-      <c r="G6">
-        <v>3.57</v>
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7.1</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5589,10 +5465,10 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
@@ -5601,7 +5477,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5610,7 +5486,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>28</v>
@@ -5621,19 +5497,19 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5678,513 +5554,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920331</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920332</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920333</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>21330051920334</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920335</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>21330051920137</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920336</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920338</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>21330051920339</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920340</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920343</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920341</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920342</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920343</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>21330051920344</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21330051920345</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330061460280</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21330051920347</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920348</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>21330051920349</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051920350</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21330051920149</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21330051920351</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>21330051920322</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920174</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>21330051920352</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>101</v>
-      </c>
-      <c r="D27" t="s">
-        <v>128</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>21330051920353</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" t="s">
-        <v>129</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>21330051920354</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" t="s">
-        <v>130</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6220,13 +5589,13 @@
         <v>21330051920332</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6243,13 +5612,13 @@
         <v>21330051920332</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6266,13 +5635,13 @@
         <v>21330051920149</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6289,13 +5658,13 @@
         <v>21330051920149</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -6312,13 +5681,13 @@
         <v>21330051920331</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6335,13 +5704,13 @@
         <v>21330051920335</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -6358,13 +5727,13 @@
         <v>21330051920137</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6381,13 +5750,13 @@
         <v>21330051920336</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -6404,13 +5773,13 @@
         <v>21330051920340</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6427,13 +5796,13 @@
         <v>21330051920347</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -6450,13 +5819,13 @@
         <v>21330051920353</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>

--- a/grupos/4APM - Estadisticos 20222.xlsx
+++ b/grupos/4APM - Estadisticos 20222.xlsx
@@ -185,13 +185,13 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
     <t>Medina Tolentino Elio</t>
@@ -820,7 +820,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -862,7 +862,7 @@
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -909,7 +909,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -998,7 +998,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1087,7 +1087,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1129,7 +1129,7 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>8</v>
@@ -1176,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1354,7 +1354,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1443,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1485,7 +1485,7 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -1532,7 +1532,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1621,7 +1621,7 @@
         <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1710,7 +1710,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1799,7 +1799,7 @@
         <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1841,7 +1841,7 @@
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>8</v>
@@ -1888,7 +1888,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1930,7 +1930,7 @@
         <v>9</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>8</v>
@@ -1977,7 +1977,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2066,7 +2066,7 @@
         <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2155,7 +2155,7 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2297,7 +2297,7 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2339,7 +2339,7 @@
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2386,7 +2386,7 @@
         <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2428,7 +2428,7 @@
         <v>9</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB22">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2517,7 +2517,7 @@
         <v>8</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2564,7 +2564,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2653,7 +2653,7 @@
         <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2695,7 +2695,7 @@
         <v>7</v>
       </c>
       <c r="AA25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -2742,7 +2742,7 @@
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2831,7 +2831,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2920,7 +2920,7 @@
         <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3098,7 +3098,7 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3140,7 +3140,7 @@
         <v>7</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>8</v>
@@ -3187,7 +3187,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3398,7 +3398,7 @@
         <v>94.3</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>85.7</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>85.7</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3670,7 +3670,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3806,7 +3806,7 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3942,7 +3942,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4010,7 +4010,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4078,7 +4078,7 @@
         <v>94.3</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4146,7 +4146,7 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4214,7 +4214,7 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>94.3</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4418,7 +4418,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4527,7 +4527,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4663,7 +4663,7 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4799,7 +4799,7 @@
         <v>85.7</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4867,7 +4867,7 @@
         <v>85.7</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4935,7 +4935,7 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5003,7 +5003,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5139,7 +5139,7 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5207,7 +5207,7 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5355,28 +5355,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>92.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5387,7 +5387,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -5408,7 +5408,7 @@
         <v>7.1</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5419,28 +5419,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>26</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>92.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="G6" s="2">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5486,7 +5486,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>28</v>
@@ -5624,7 +5624,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>

--- a/grupos/4APM - Estadisticos 20222.xlsx
+++ b/grupos/4APM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -215,6 +215,9 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>ABAD</t>
   </si>
   <si>
@@ -224,45 +227,45 @@
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>SOL</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>ISRAEL</t>
   </si>
   <si>
     <t>JOSELIN</t>
   </si>
   <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
     <t>MARITZA</t>
   </si>
   <si>
@@ -275,13 +278,13 @@
     <t>YAIR DAVID</t>
   </si>
   <si>
-    <t>DARLET VICTORIA</t>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JOCELIN</t>
   </si>
   <si>
     <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
   </si>
 </sst>
 </file>
@@ -811,7 +814,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -823,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -900,7 +903,7 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>9</v>
@@ -912,7 +915,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -989,7 +992,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -1001,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>9</v>
@@ -1078,7 +1081,7 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -1090,7 +1093,7 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1167,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>8</v>
@@ -1179,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1221,7 +1224,7 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -1256,7 +1259,7 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -1268,7 +1271,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1310,7 +1313,7 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1345,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>9</v>
@@ -1357,7 +1360,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -1434,7 +1437,7 @@
         <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -1446,7 +1449,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -1523,7 +1526,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -1535,7 +1538,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -1565,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1612,7 +1615,7 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>9</v>
@@ -1624,7 +1627,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -1654,7 +1657,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1701,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>7</v>
@@ -1713,7 +1716,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -1743,7 +1746,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1790,7 +1793,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -1802,7 +1805,7 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>7</v>
@@ -1879,7 +1882,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -1891,7 +1894,7 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>7</v>
@@ -1968,7 +1971,7 @@
         <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>9</v>
@@ -1980,7 +1983,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -2022,7 +2025,7 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2057,7 +2060,7 @@
         <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -2069,7 +2072,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -2099,7 +2102,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2146,7 +2149,7 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>9</v>
@@ -2158,7 +2161,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -2188,7 +2191,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2288,7 +2291,7 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -2300,7 +2303,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2377,7 +2380,7 @@
         <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>10</v>
@@ -2389,7 +2392,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -2466,7 +2469,7 @@
         <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -2478,7 +2481,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2555,7 +2558,7 @@
         <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>8</v>
@@ -2567,7 +2570,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>10</v>
@@ -2644,7 +2647,7 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -2656,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2733,7 +2736,7 @@
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -2745,7 +2748,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -2787,7 +2790,7 @@
         <v>10</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -2822,7 +2825,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -2834,7 +2837,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>8</v>
@@ -2864,7 +2867,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2911,7 +2914,7 @@
         <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>9</v>
@@ -2923,7 +2926,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -2953,7 +2956,7 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -3000,7 +3003,7 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>10</v>
@@ -3012,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -3089,7 +3092,7 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>7</v>
@@ -3101,7 +3104,7 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -3131,7 +3134,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3178,7 +3181,7 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>10</v>
@@ -3190,7 +3193,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>10</v>
@@ -3389,7 +3392,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K4">
         <v>93.3</v>
@@ -3401,7 +3404,7 @@
         <v>120</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
         <v>106.7</v>
@@ -3457,7 +3460,7 @@
         <v>85</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K5">
         <v>96.7</v>
@@ -3469,7 +3472,7 @@
         <v>120</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>106.7</v>
@@ -3525,7 +3528,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K6">
         <v>90</v>
@@ -3537,7 +3540,7 @@
         <v>120</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
         <v>106.7</v>
@@ -3593,7 +3596,7 @@
         <v>85</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K7">
         <v>83.3</v>
@@ -3605,7 +3608,7 @@
         <v>120</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
         <v>106.7</v>
@@ -3661,7 +3664,7 @@
         <v>85</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3673,7 +3676,7 @@
         <v>120</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
         <v>106.7</v>
@@ -3729,7 +3732,7 @@
         <v>85</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3741,7 +3744,7 @@
         <v>120</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
         <v>106.7</v>
@@ -3797,7 +3800,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -3809,7 +3812,7 @@
         <v>120</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
         <v>106.7</v>
@@ -3865,7 +3868,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K11">
         <v>96.7</v>
@@ -3877,7 +3880,7 @@
         <v>120</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
         <v>106.7</v>
@@ -3933,7 +3936,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3945,7 +3948,7 @@
         <v>120</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
         <v>106.7</v>
@@ -4001,7 +4004,7 @@
         <v>85</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K13">
         <v>93.3</v>
@@ -4013,7 +4016,7 @@
         <v>120</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
         <v>106.7</v>
@@ -4069,7 +4072,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -4081,7 +4084,7 @@
         <v>120</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
         <v>106.7</v>
@@ -4137,7 +4140,7 @@
         <v>85</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K15">
         <v>96.7</v>
@@ -4149,7 +4152,7 @@
         <v>120</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
         <v>106.7</v>
@@ -4205,7 +4208,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K16">
         <v>96.7</v>
@@ -4217,7 +4220,7 @@
         <v>120</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
         <v>106.7</v>
@@ -4273,7 +4276,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -4285,7 +4288,7 @@
         <v>120</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
         <v>106.7</v>
@@ -4341,7 +4344,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -4353,7 +4356,7 @@
         <v>120</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
         <v>106.7</v>
@@ -4409,7 +4412,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K19">
         <v>96.7</v>
@@ -4421,7 +4424,7 @@
         <v>120</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
         <v>106.7</v>
@@ -4518,7 +4521,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K21">
         <v>96.7</v>
@@ -4530,7 +4533,7 @@
         <v>120</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
         <v>106.7</v>
@@ -4586,7 +4589,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K22">
         <v>96.7</v>
@@ -4598,7 +4601,7 @@
         <v>120</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
         <v>106.7</v>
@@ -4654,7 +4657,7 @@
         <v>85</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K23">
         <v>93.3</v>
@@ -4666,7 +4669,7 @@
         <v>120</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
         <v>106.7</v>
@@ -4722,7 +4725,7 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4734,7 +4737,7 @@
         <v>120</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
         <v>106.7</v>
@@ -4790,7 +4793,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K25">
         <v>96.7</v>
@@ -4802,7 +4805,7 @@
         <v>120</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
         <v>106.7</v>
@@ -4858,7 +4861,7 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K26">
         <v>93.3</v>
@@ -4870,7 +4873,7 @@
         <v>120</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
         <v>106.7</v>
@@ -4926,7 +4929,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K27">
         <v>93.3</v>
@@ -4938,7 +4941,7 @@
         <v>120</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
         <v>106.7</v>
@@ -4994,7 +4997,7 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K28">
         <v>96.7</v>
@@ -5006,7 +5009,7 @@
         <v>120</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
         <v>106.7</v>
@@ -5062,7 +5065,7 @@
         <v>70</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K29">
         <v>93.3</v>
@@ -5074,7 +5077,7 @@
         <v>120</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
         <v>106.7</v>
@@ -5130,7 +5133,7 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K30">
         <v>96.7</v>
@@ -5142,7 +5145,7 @@
         <v>120</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
         <v>106.7</v>
@@ -5198,7 +5201,7 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -5210,7 +5213,7 @@
         <v>120</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
         <v>106.7</v>
@@ -5300,19 +5303,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>66.7</v>
+        <v>59.3</v>
       </c>
       <c r="G2" s="2">
-        <v>33.3</v>
+        <v>40.7</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5472,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5554,7 +5557,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5592,7 +5595,7 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
         <v>79</v>
@@ -5615,7 +5618,7 @@
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
         <v>79</v>
@@ -5638,7 +5641,7 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
         <v>80</v>
@@ -5661,7 +5664,7 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
         <v>80</v>
@@ -5678,13 +5681,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920331</v>
+        <v>21330051920353</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
         <v>81</v>
@@ -5701,22 +5704,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920335</v>
+        <v>21330051920353</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5724,16 +5727,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920137</v>
+        <v>21330051920331</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
         <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5747,16 +5750,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920336</v>
+        <v>21330051920335</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5770,16 +5773,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920340</v>
+        <v>21330051920137</v>
       </c>
       <c r="B10" t="s">
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5793,16 +5796,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920347</v>
+        <v>21330051920336</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5816,24 +5819,70 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920353</v>
+        <v>20330051920343</v>
       </c>
       <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920345</v>
+      </c>
+      <c r="B13" t="s">
         <v>70</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920347</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
         <v>78</v>
       </c>
-      <c r="D12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
+      <c r="D14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APM - Estadisticos 20222.xlsx
+++ b/grupos/4APM - Estadisticos 20222.xlsx
@@ -3371,7 +3371,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>96.7</v>
@@ -3386,49 +3386,49 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>100</v>
       </c>
       <c r="J4">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="L4">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3439,7 +3439,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -3454,49 +3454,49 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I5">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J5">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3507,7 +3507,7 @@
         <v>95</v>
       </c>
       <c r="C6">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -3522,49 +3522,49 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J6">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L6">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3575,7 +3575,7 @@
         <v>70</v>
       </c>
       <c r="C7">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>86.7</v>
@@ -3590,49 +3590,49 @@
         <v>30</v>
       </c>
       <c r="H7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I7">
+        <v>77.5</v>
+      </c>
+      <c r="J7">
+        <v>87.3</v>
+      </c>
+      <c r="K7">
         <v>85</v>
-      </c>
-      <c r="J7">
-        <v>90</v>
-      </c>
-      <c r="K7">
-        <v>83.3</v>
       </c>
       <c r="L7">
         <v>85.7</v>
       </c>
       <c r="M7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="O7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>87.3</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3643,7 +3643,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -3658,13 +3658,13 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I8">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J8">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3673,34 +3673,34 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3711,7 +3711,7 @@
         <v>95</v>
       </c>
       <c r="C9">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -3726,13 +3726,13 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J9">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3741,34 +3741,34 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3779,7 +3779,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -3794,13 +3794,13 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>100</v>
       </c>
       <c r="J10">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -3809,34 +3809,34 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3847,7 +3847,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -3862,49 +3862,49 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3915,7 +3915,7 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -3930,13 +3930,13 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>100</v>
       </c>
       <c r="J12">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3945,34 +3945,34 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3983,7 +3983,7 @@
         <v>85</v>
       </c>
       <c r="C13">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>93.3</v>
@@ -3998,49 +3998,49 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>85</v>
       </c>
       <c r="J13">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>93.3</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4051,7 +4051,7 @@
         <v>95</v>
       </c>
       <c r="C14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -4066,49 +4066,49 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J14">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4119,7 +4119,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -4134,49 +4134,49 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I15">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4187,7 +4187,7 @@
         <v>95</v>
       </c>
       <c r="C16">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>96.7</v>
@@ -4202,13 +4202,13 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J16">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>96.7</v>
@@ -4217,34 +4217,34 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4255,7 +4255,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -4270,13 +4270,13 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -4285,34 +4285,34 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N17">
         <v>100</v>
       </c>
       <c r="O17">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4323,7 +4323,7 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -4338,49 +4338,49 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
       <c r="J18">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4391,7 +4391,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -4406,49 +4406,49 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>100</v>
       </c>
       <c r="J19">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4465,31 +4465,31 @@
         <v>80</v>
       </c>
       <c r="H20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K20">
         <v>83.3</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4500,7 +4500,7 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -4515,49 +4515,49 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>100</v>
       </c>
       <c r="J21">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K21">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L21">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N21">
         <v>100</v>
       </c>
       <c r="O21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4568,7 +4568,7 @@
         <v>85</v>
       </c>
       <c r="C22">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -4583,49 +4583,49 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="J22">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N22">
         <v>100</v>
       </c>
       <c r="O22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4636,7 +4636,7 @@
         <v>85</v>
       </c>
       <c r="C23">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>93.3</v>
@@ -4651,49 +4651,49 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>85</v>
       </c>
       <c r="J23">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>93.3</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N23">
         <v>100</v>
       </c>
       <c r="O23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4704,7 +4704,7 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -4719,13 +4719,13 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>100</v>
       </c>
       <c r="J24">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4734,34 +4734,34 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4772,7 +4772,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -4787,49 +4787,49 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>100</v>
       </c>
       <c r="J25">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L25">
-        <v>85.7</v>
+        <v>90</v>
       </c>
       <c r="M25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N25">
         <v>100</v>
       </c>
       <c r="O25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -4840,7 +4840,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -4855,49 +4855,49 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I26">
         <v>100</v>
       </c>
       <c r="J26">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L26">
-        <v>85.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N26">
         <v>100</v>
       </c>
       <c r="O26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -4908,7 +4908,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -4923,49 +4923,49 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
       </c>
       <c r="J27">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N27">
         <v>100</v>
       </c>
       <c r="O27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -4976,7 +4976,7 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>96.7</v>
@@ -4991,13 +4991,13 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>100</v>
       </c>
       <c r="J28">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>96.7</v>
@@ -5006,34 +5006,34 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N28">
         <v>100</v>
       </c>
       <c r="O28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5044,7 +5044,7 @@
         <v>85</v>
       </c>
       <c r="C29">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -5059,49 +5059,49 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I29">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="J29">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K29">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N29">
         <v>100</v>
       </c>
       <c r="O29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5112,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -5127,49 +5127,49 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>100</v>
       </c>
       <c r="J30">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>100</v>
       </c>
       <c r="O30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5180,7 +5180,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -5195,13 +5195,13 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -5210,34 +5210,34 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>100</v>
       </c>
       <c r="O31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4APM - Estadisticos 20222.xlsx
+++ b/grupos/4APM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="80">
   <si>
     <t>Materia</t>
   </si>
@@ -185,18 +185,18 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,82 +209,55 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>AVELLEIRA</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RICO</t>
   </si>
   <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SOL</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>JUAREZ</t>
   </si>
   <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
+    <t>JOSELIN</t>
   </si>
   <si>
     <t>ISRAEL</t>
   </si>
   <si>
-    <t>JOSELIN</t>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>AMIR ALONSO</t>
   </si>
   <si>
     <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JOCELIN</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -832,22 +805,22 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -856,7 +829,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -865,7 +838,7 @@
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -921,34 +894,34 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z5">
         <v>8</v>
@@ -1010,22 +983,22 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1034,13 +1007,13 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>5</v>
@@ -1099,22 +1072,22 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1126,16 +1099,16 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1188,22 +1161,22 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1224,7 +1197,7 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -1277,22 +1250,22 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1301,10 +1274,10 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>9</v>
@@ -1313,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1366,22 +1339,22 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1390,13 +1363,13 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1455,22 +1428,22 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1485,10 +1458,10 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -1544,22 +1517,22 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1568,7 +1541,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1633,28 +1606,28 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1663,10 +1636,10 @@
         <v>8</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>8</v>
@@ -1722,22 +1695,22 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1746,7 +1719,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1755,7 +1728,7 @@
         <v>8</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -1811,22 +1784,22 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1900,22 +1873,22 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1924,10 +1897,10 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z16">
         <v>9</v>
@@ -1989,22 +1962,22 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2022,7 +1995,7 @@
         <v>8</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>9</v>
@@ -2078,22 +2051,22 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2111,7 +2084,7 @@
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>8</v>
@@ -2167,40 +2140,40 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB19">
         <v>8</v>
@@ -2238,19 +2211,19 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2309,28 +2282,28 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2342,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2398,22 +2371,22 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2422,13 +2395,13 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2487,22 +2460,22 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2511,16 +2484,16 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>8</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2576,22 +2549,22 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2606,7 +2579,7 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA24">
         <v>9</v>
@@ -2665,28 +2638,28 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2698,7 +2671,7 @@
         <v>7</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -2754,43 +2727,43 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -2843,22 +2816,22 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2867,10 +2840,10 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z27">
         <v>10</v>
@@ -2932,22 +2905,22 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -2959,7 +2932,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>9</v>
@@ -3021,22 +2994,22 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -3054,7 +3027,7 @@
         <v>10</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29">
         <v>10</v>
@@ -3110,34 +3083,34 @@
         <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>7</v>
@@ -3199,22 +3172,22 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3416,10 +3389,10 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="S4">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -3478,13 +3451,13 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R5">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3546,16 +3519,16 @@
         <v>100</v>
       </c>
       <c r="P6">
+        <v>95.3</v>
+      </c>
+      <c r="Q6">
         <v>97.5</v>
       </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
       <c r="R6">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S6">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -3614,22 +3587,22 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>77.5</v>
+        <v>82.8</v>
       </c>
       <c r="Q7">
-        <v>87.3</v>
+        <v>60</v>
       </c>
       <c r="R7">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="S7">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="T7">
         <v>100</v>
       </c>
       <c r="U7">
-        <v>65</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3682,10 +3655,10 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -3750,7 +3723,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3892,7 +3865,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4022,16 +3995,16 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R13">
-        <v>93.3</v>
+        <v>94.8</v>
       </c>
       <c r="S13">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -4090,16 +4063,16 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S14">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -4158,13 +4131,13 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>98.3</v>
+        <v>95.8</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4226,13 +4199,13 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4371,7 +4344,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -4436,7 +4409,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4480,13 +4453,13 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>90</v>
+        <v>70.3</v>
       </c>
       <c r="R20">
-        <v>83.3</v>
+        <v>54.2</v>
       </c>
       <c r="S20">
-        <v>90</v>
+        <v>64.3</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4542,13 +4515,13 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R21">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S21">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -4607,13 +4580,13 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4675,16 +4648,16 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>93.3</v>
+        <v>94.8</v>
       </c>
       <c r="S23">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -4814,13 +4787,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="R25">
-        <v>98.3</v>
+        <v>95.8</v>
       </c>
       <c r="S25">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -4882,19 +4855,19 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R26">
-        <v>96.7</v>
+        <v>94.8</v>
       </c>
       <c r="S26">
-        <v>88.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="T26">
         <v>100</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -4953,7 +4926,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5021,7 +4994,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5083,16 +5056,16 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>77.5</v>
+        <v>82.8</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>96.7</v>
+        <v>94.8</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5157,7 +5130,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5303,19 +5276,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>59.3</v>
+        <v>85.2</v>
       </c>
       <c r="G2" s="2">
-        <v>40.7</v>
+        <v>14.8</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5358,28 +5331,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>92.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5390,28 +5363,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>92.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5422,28 +5395,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6">
+        <v>28</v>
+      </c>
+      <c r="D6">
         <v>27</v>
-      </c>
-      <c r="D6">
-        <v>26</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>96.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5454,28 +5427,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>27</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5486,28 +5459,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>28</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5557,7 +5530,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5589,16 +5562,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920332</v>
+        <v>21330051920149</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5612,22 +5585,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920332</v>
+        <v>21330051920149</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5635,22 +5608,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920149</v>
+        <v>21330051920332</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5658,22 +5631,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920149</v>
+        <v>21330051920137</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5681,16 +5654,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920353</v>
+        <v>21330051920347</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5704,22 +5677,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920353</v>
+        <v>21330051920351</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5727,162 +5700,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920331</v>
+        <v>21330051920353</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920335</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920137</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920336</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920343</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920345</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920347</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APM - Estadisticos 20222.xlsx
+++ b/grupos/4APM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="77">
   <si>
     <t>Materia</t>
   </si>
@@ -224,9 +224,6 @@
     <t>RICO</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>JOSELIN</t>
   </si>
   <si>
@@ -255,9 +249,6 @@
   </si>
   <si>
     <t>AMIR ALONSO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
   </si>
 </sst>
 </file>
@@ -823,7 +814,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -912,7 +903,7 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -933,7 +924,7 @@
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1001,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1022,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1090,7 +1081,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1179,7 +1170,7 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1268,7 +1259,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1357,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1446,7 +1437,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1535,7 +1526,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1624,7 +1615,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1713,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1802,7 +1793,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1891,7 +1882,7 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1980,7 +1971,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2069,7 +2060,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2158,7 +2149,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2220,7 +2211,7 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2300,7 +2291,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2321,7 +2312,7 @@
         <v>8</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2389,7 +2380,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2478,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2567,7 +2558,7 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2588,7 +2579,7 @@
         <v>8</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2656,7 +2647,7 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2745,7 +2736,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2766,7 +2757,7 @@
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2834,7 +2825,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2923,7 +2914,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -3012,7 +3003,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -3101,7 +3092,7 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3122,7 +3113,7 @@
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3190,7 +3181,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -5308,16 +5299,16 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="G3" s="2">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -5530,7 +5521,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5568,10 +5559,10 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5591,10 +5582,10 @@
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -5614,10 +5605,10 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5637,10 +5628,10 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -5660,10 +5651,10 @@
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5683,10 +5674,10 @@
         <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5695,29 +5686,6 @@
         <v>56</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920353</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>
